--- a/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 5,91</t>
+          <t>-5,41; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 8,39</t>
+          <t>-3,72; 10,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,8</t>
+          <t>-2,47; 2,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,44</t>
+          <t>-1,95; 3,51</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,22</t>
+          <t>-0,66; 3,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,39</t>
+          <t>0,19; 4,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,07</t>
+          <t>-1,53; 2,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,99</t>
+          <t>-1,53; 2,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,89</t>
+          <t>-0,66; 2,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,53</t>
+          <t>-0,07; 2,62</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,75; —</t>
+          <t>-18,28; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 358,6</t>
+          <t>-66,4; 401,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,69; 326,0</t>
+          <t>-76,67; 369,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,71; 292,3</t>
+          <t>-46,95; 354,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 367,38</t>
+          <t>-17,26; 452,16</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,05</t>
+          <t>0,52; 8,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,14</t>
+          <t>-1,8; 3,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,39</t>
+          <t>0,79; 7,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,29</t>
+          <t>0,7; 5,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,48</t>
+          <t>1,25; 6,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,5</t>
+          <t>-0,07; 3,8</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,45</t>
+          <t>0,2; 3,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,32</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,22</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,12</t>
+          <t>-0,69; 2,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,3</t>
+          <t>0,15; 2,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,27</t>
+          <t>0,05; 2,28</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 902,71</t>
+          <t>-7,26; 948,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 836,63</t>
+          <t>-10,95; 904,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 522,94</t>
+          <t>-47,01; 524,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,87; 496,75</t>
+          <t>-52,76; 479,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 421,86</t>
+          <t>0,5; 370,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 411,11</t>
+          <t>-11,9; 346,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 5,42</t>
+          <t>-4,34; 5,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 10,24</t>
+          <t>-3,76; 9,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,84</t>
+          <t>-2,54; 2,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,51</t>
+          <t>-1,96; 3,5</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,19</t>
+          <t>-0,61; 2,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,19</t>
+          <t>0,2; 4,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,11</t>
+          <t>-1,43; 2,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,05</t>
+          <t>-1,93; 2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,11</t>
+          <t>-0,53; 2,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,62</t>
+          <t>-0,16; 2,7</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,28; —</t>
+          <t>-25,11; 1561,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,4; 401,83</t>
+          <t>-70,01; 371,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,67; 369,63</t>
+          <t>-85,51; 310,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 354,43</t>
+          <t>-37,96; 409,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 452,16</t>
+          <t>-19,86; 448,46</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 8,83</t>
+          <t>0,53; 8,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,07</t>
+          <t>-1,79; 3,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,26</t>
+          <t>0,8; 7,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,92</t>
+          <t>0,7; 7,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,23</t>
+          <t>1,25; 7,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,8</t>
+          <t>-0,14; 3,56</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,51</t>
+          <t>0,31; 3,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,05; 3,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,53; 2,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,13</t>
+          <t>-0,55; 2,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,31</t>
+          <t>0,17; 2,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,28</t>
+          <t>0,1; 2,17</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 948,17</t>
+          <t>-12,08; 812,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 904,66</t>
+          <t>-22,92; 717,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 524,91</t>
+          <t>-51,66; 594,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 479,87</t>
+          <t>-52,98; 707,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 370,74</t>
+          <t>1,89; 396,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 346,45</t>
+          <t>-7,59; 410,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,69</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 5,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 9,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,11; 5,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,73; 8,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,83</t>
+          <t>-2,92; 2,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,5</t>
+          <t>-1,96; 3,44</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>41,82%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>37,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,9</t>
+          <t>-1,59; 2,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,21</t>
+          <t>-1,75; 1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,14</t>
+          <t>-0,59; 3,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,0</t>
+          <t>0,37; 4,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,22</t>
+          <t>-0,67; 1,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,7</t>
+          <t>-0,17; 2,53</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>114,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>246,97%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,07; 358,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 1561,35</t>
+          <t>-83,69; 326,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,01; 371,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,51; 310,26</t>
+          <t>-19,75; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 409,69</t>
+          <t>-50,71; 292,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 448,46</t>
+          <t>-22,27; 367,38</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>3,98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,66</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 8,97</t>
+          <t>0,79; 6,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,07</t>
+          <t>0,7; 6,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,56</t>
+          <t>0,55; 9,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,26</t>
+          <t>-1,79; 3,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,28</t>
+          <t>1,34; 6,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,56</t>
+          <t>-0,12; 3,5</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>476,53%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>79,12%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,55</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,54</t>
+          <t>-0,61; 2,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,53</t>
+          <t>-0,66; 2,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,18</t>
+          <t>0,2; 3,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,36</t>
+          <t>0,14; 3,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,22</t>
+          <t>0,17; 2,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,17</t>
+          <t>0,09; 2,27</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>71,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>171,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>160,17%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>74,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>71,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 812,05</t>
+          <t>-54,01; 522,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 717,05</t>
+          <t>-54,87; 496,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 594,21</t>
+          <t>-5,47; 902,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 707,1</t>
+          <t>-15,93; 836,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 396,99</t>
+          <t>5,29; 421,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 410,21</t>
+          <t>2,03; 411,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,277 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7778091312979657</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.6881152339016798</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.4196578852186382</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.1501975768029251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 5,91</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,73; 8,39</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,92; 2,8</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,96; 3,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>-4.111365792775943</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.725807505428785</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.915743763346489</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.955582043783502</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>43,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>5.912919042994017</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.392418425272123</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.799248494863747</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3.444839673360739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>0.4182464300505868</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.370015892668339</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4319156147273991</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1545846771867589</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,59; 2,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,75; 1,99</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,59; 3,22</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 4,39</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 1,89</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 2,53</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>114,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>246,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2590433104574684</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1723001181946361</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9452621142995921</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.035450096501829</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.5892804385868559</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.093327634327165</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-74,07; 358,6</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-83,69; 326,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-19,75; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-50,71; 292,3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-22,27; 367,38</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.592366868748132</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.749461199843993</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.5884075850427812</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.3727205916299407</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.6720647415300863</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.1736710660874497</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.069668990797747</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.988410689011726</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.222199992033624</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.389895833455194</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.886796594156835</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.533248851199278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,79; 6,39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,7; 6,29</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,55; 9,05</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 3,14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 6,48</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,12; 3,5</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.180235679113696</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.1198819948654072</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1.146944901715278</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2.469737309432386</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.5160277354332717</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.9574174642237101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>476,53%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>79,12%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>777,5%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>357,04%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.7407302039985654</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.8369018785713609</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="n">
+        <v>-0.1975265182762654</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5070803808675364</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2226891569491178</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>3.585997820521713</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>3.259971677351015</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>2.923002973179014</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.673838702485752</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +878,297 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>2.595078199120835</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.387485859053062</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.980422713552381</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.660921291193578</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.303214146835229</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.516895781343306</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 2,22</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 2,12</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 3,45</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 3,32</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 2,3</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 2,27</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.7945591157267964</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.700089321421832</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5516515804653509</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.786650495074059</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.339191797103424</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.1225384074011681</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>74,0%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>71,24%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>171,83%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>160,17%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>121,82%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>115,11%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.38734930860221</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.286569986207104</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.047342583437867</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.140657734871674</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>6.482231063556288</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.50301821850791</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-54,01; 522,94</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-54,87; 496,75</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-5,47; 902,71</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-15,93; 836,63</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5,29; 421,86</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 411,11</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>4.765267870811527</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.7912393282594961</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>7.775009137359207</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>3.570425057565648</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.7225249860955182</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.695532575977429</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.658203470961065</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.545653623089633</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.18256804613872</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1.117413018549899</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.6096631713909123</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6646622584323106</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.2044589435158876</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.1379348176310226</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.1710972007816692</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.09110288911038003</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.216811441938253</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.123603684693607</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.446897890021002</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.324627044283745</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2.303116291547234</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2.273741455497742</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.7400493640307353</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.7124022703994185</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1.718293149296476</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1.601664740335449</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1.218187518774584</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1.151069992934718</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.5400517330004698</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.5486576702707947</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.0546708153344117</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.1593177301444079</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.05288459803580207</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.02031992606440861</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5.229407420303307</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4.967496921317743</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>9.027091578427576</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>8.366296308371933</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>4.218556290745711</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>4.111148646527813</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1176,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
